--- a/step7-图片内容分析和注释模板_0608.xlsx
+++ b/step7-图片内容分析和注释模板_0608.xlsx
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="156">
   <si>
     <t>模块ID</t>
   </si>
@@ -100,9 +100,6 @@
   </si>
   <si>
     <t>净利润的贡献 - 保险服务业绩和投资服务业绩</t>
-  </si>
-  <si>
-    <t>各公司同口径新准则下投资利润和保险利润，其中中国人寿的投资利润占净利润的比例较高，太平人寿的保险利润占净利润的比例较高。</t>
   </si>
   <si>
     <t>此处保险服务业绩仅包括原保险。</t>
@@ -123,9 +120,6 @@
     <t>税前利润、税率及净利润</t>
   </si>
   <si>
-    <t>随着2025年底新税法的实施，部分头部公司所得税金额变动较大，太平人寿在2025年产生了税项抵免</t>
-  </si>
-  <si>
     <t>太平人寿释放了之前计提的税亏型递延所得税资产（但也同时计提了更多的税亏型递延所得税资产）</t>
   </si>
   <si>
@@ -143,9 +137,6 @@
     <t>净利润 = 保险利润+投资利润+其他利润（主要包括其他业务收入、营业外收支和所得税费用等）。</t>
   </si>
   <si>
-    <t>除人保寿险外，其余8家头部寿险公司净利润均有所上升，其中太平人寿增长最快。</t>
-  </si>
-  <si>
     <t>a家上升&amp;增幅最大值、
 b家下降&amp;降幅最大值</t>
   </si>
@@ -163,9 +154,6 @@
 寿险保费中投资成分占比较大，所以寿险保费不能计入保险服务收入的比例较高。</t>
   </si>
   <si>
-    <t>除平安人寿外，其余8家头部保险公司保险服务收入均有所上升。</t>
-  </si>
-  <si>
     <t>此处仅包括原保险业务收入。</t>
   </si>
   <si>
@@ -180,9 +168,6 @@
   </si>
   <si>
     <t>2025年和2024年收入构成比例基本稳定</t>
-  </si>
-  <si>
-    <t>中国人寿采用保险分配法的保险服务收入占比最高；平安人寿未采用保费分配法的保险服务收入占比最高。</t>
   </si>
   <si>
     <t>a家主要构成部分为x（x是多数公司的最大构成部分）、
@@ -216,9 +201,6 @@
     </r>
   </si>
   <si>
-    <t>友邦人寿合同服务边际释放占比最高；新华人寿预期保险服务费用占比最高；阳光人寿保险获取现金流的摊销占比最高。</t>
-  </si>
-  <si>
     <t>exp_total</t>
   </si>
   <si>
@@ -226,9 +208,6 @@
   </si>
   <si>
     <t>新准则调整保险服务费用的确认原则：剔除投资成分、收入在提供服务的保险期间逐期确认。</t>
-  </si>
-  <si>
-    <t>除中国人寿和平安人寿外，其余7家头部寿险公司保险服务费用均有所上升，其中人保寿险增长最快。</t>
   </si>
   <si>
     <t>人保寿险的保险服务费用大幅增加，增加100亿里面80亿来自于亏损确认及转回（去年是50亿亏损转回，今年是30亿亏损确认，不是新业务造成，新业务去年5亿LC NB，今年10亿）</t>
@@ -266,9 +245,6 @@
     <t>业务及管理费（新准则分类）</t>
   </si>
   <si>
-    <t>泰康人寿获取费用占比最高，同时非履约占比最低；太保寿险维持费用占比最高，同时获取费用占比最低；友邦人寿非履约费用占比最高。</t>
-  </si>
-  <si>
     <t>此处非履约费用仅采用公司口径。</t>
   </si>
   <si>
@@ -279,9 +255,6 @@
   </si>
   <si>
     <t>保险服务业绩=保险服务收入–保险服务费用。</t>
-  </si>
-  <si>
-    <t>2025年6家头部保险公司整体保险利润相较于2024同期总体有所上升，其中中国人寿增长最快。</t>
   </si>
   <si>
     <t>年报披露数据计算的非履约比例和实际精算假设认存在差异。以太平人寿为例，假设仅2%，会剔除委托管理费里面的投资费用。</t>
@@ -313,9 +286,6 @@
     </r>
   </si>
   <si>
-    <t>合同服务边际释放贡献平均占比为96%。</t>
-  </si>
-  <si>
     <t>国寿基本没有什么营运偏差，或者有不利偏差的都在LC中出来了。</t>
   </si>
   <si>
@@ -351,9 +321,6 @@
     </r>
   </si>
   <si>
-    <t>合同服务边际释放贡献平均占比为102%。</t>
-  </si>
-  <si>
     <t>inv_return</t>
   </si>
   <si>
@@ -366,9 +333,6 @@
     <t>净投资回报=利息收入+投资收益+公允价值变动+汇兑损益-利息支出-其他资产减值损失 - 信用减值损失。</t>
   </si>
   <si>
-    <t>除太平人寿轻微下降外，其余8家寿险公司净投资回报均有所上升。</t>
-  </si>
-  <si>
     <t>uw_profit</t>
   </si>
   <si>
@@ -378,9 +342,6 @@
     <t>承保财务净损益 = 承保财务损益 - 分出再保险财务损益。</t>
   </si>
   <si>
-    <t>除太平人寿和友邦人寿下降外，其余7家寿险公司承保财务净损益均有所上升，其中泰康人寿增长最快。</t>
-  </si>
-  <si>
     <t>太平人寿承保财务损益下降和主推分红产品+有效久期缺口收窄有关</t>
   </si>
   <si>
@@ -390,9 +351,6 @@
     <t>投资利润 = 净投资回报 – 承保财务净损益。</t>
   </si>
   <si>
-    <t>除人保寿险和阳光人寿外，其余7家头部寿险公司投资利润均有所上升，其中太平人寿增长最快。</t>
-  </si>
-  <si>
     <t>oci_profit</t>
   </si>
   <si>
@@ -400,9 +358,6 @@
   </si>
   <si>
     <t>其他综合收益</t>
-  </si>
-  <si>
-    <t>除阳光人寿和太保寿险外，其余7家保险公司其他综合收益均有所回升。人保寿险增长幅度最大，太保寿险下降幅度最大。</t>
   </si>
   <si>
     <t>oci_deep</t>
@@ -422,10 +377,6 @@
   <si>
     <t xml:space="preserve">2025年末当日国债收益率曲线较2024年末当日曲线呈一定幅度的上升。已披露公司在2025年FVOCI债券公允价值的负向波动均大于负债端OCI的正向波动。
 </t>
-  </si>
-  <si>
-    <t>2025年大部分头部寿险子公司仍增配了FVOCI股权类投资，使得净利润更加平稳，其波动计入其他综合收益。
-除阳光人寿外，已披露公司在2025年的OCI缺口较2024年均有所减小。</t>
   </si>
   <si>
     <t>【OCI缺口】
@@ -445,9 +396,6 @@
     <t>综合收益总额 = 净利润+其他综合收益。</t>
   </si>
   <si>
-    <t>除阳光人寿、太保人寿受OCI缺口较去年度扩大影响，其他头部公司当年综合收益总额均较去年有所回升。</t>
-  </si>
-  <si>
     <t>阳光综合收益是负的，但是净资产增加是因为发了51亿永续债</t>
   </si>
   <si>
@@ -458,9 +406,6 @@
   </si>
   <si>
     <t>总资产</t>
-  </si>
-  <si>
-    <t>头部公司总资产较去年上升，平均上升幅度14%。</t>
   </si>
   <si>
     <t>asset_struct</t>
@@ -473,9 +418,6 @@
 新金融工具准则下，金融资产新增一项会计分类“其他权益工具投资”，即指定为公允价值计量且变动进综合收益；</t>
   </si>
   <si>
-    <t>2025年，为实现资产负债匹配和降低净利润的波动，除新华外，头部公司FVOCI债权投资的占比仍居首位；此外，在追求投资收益的同时，为使得利润平稳，上述公司在2025年对FVOCI股权类投资也均有一定的增配。</t>
-  </si>
-  <si>
     <t>2024年部分公司未重塑新金融工具准则，此页为对比演示，将I39下“以公允价值计量且其变动计入当期损益的金融资产”匹配至“交易性金融资产”；“可供出售金融资产”匹配至“其他债权投资”；“应收款项类投资”、“持有至到期投资”、“应收利息”匹配至“债权投资”。</t>
   </si>
   <si>
@@ -486,9 +428,6 @@
   </si>
   <si>
     <t>CSM 余额</t>
-  </si>
-  <si>
-    <t>2025年除平安、泰康外，头部公司合同服务边际余额均呈上升趋势。</t>
   </si>
   <si>
     <t>csm_ratio</t>
@@ -532,10 +471,6 @@
 </t>
   </si>
   <si>
-    <t>2025年，新业务CSM为增加整体CSM余额的主要驱动因素。以阳光、人保和友邦最为突出。对比2024年，CSM调整项的影响减弱。
-2025年，除泰康外，所有上市公司CSM调整为有利偏差。</t>
-  </si>
-  <si>
     <t>泰康两年CSM调整项变动巨大</t>
   </si>
   <si>
@@ -545,18 +480,10 @@
     <t>2024年摊销前 CSM 变动项占比</t>
   </si>
   <si>
-    <t>2024年，新业务CSM和CSM调整为整体CSM余额变动的主要驱动因素。阳光受新业务CSM驱动影响最大，太保和泰康受CSM调整项影响突出。
-2024年，4家头部公司为不利偏差影响，5家头部公司为有利偏差影响，泰康影响最为突出。</t>
-  </si>
-  <si>
     <t>csm_ratio_trend</t>
   </si>
   <si>
     <t>CSM趋势(摊销比率/持续率）</t>
-  </si>
-  <si>
-    <t>对比两年，CSM摊销比率基本稳定，人保、平安、太保略有下降；
-CSM持续率代表当年新业务CSM与CSM摊销金额的比率，除阳光、人保、友邦外，大多数头部公司持续率不足100%，其中，阳光人寿、太平人寿两年CSM持续率下降明显。</t>
   </si>
   <si>
     <t>CSM摊销比率=(CSM摊销/摊销前的期末CSM); CSM持续率=(新业务CSM/CSM摊销)；
@@ -574,9 +501,6 @@
   </si>
   <si>
     <t>净资产</t>
-  </si>
-  <si>
-    <t>受2025年国债收益率曲线上浮影响，头部公司净资产存在不同程度的上涨。</t>
   </si>
   <si>
     <t>净资产 = 上期末净资产+当期综合收益+其他（主要包括少数股东增资、发行债券和股东分红等）。</t>
@@ -602,16 +526,10 @@
     <t>新业务CSM</t>
   </si>
   <si>
-    <t>超半数头部公司2025年新业务CSM提升，人保寿险新业务CSM上升最多；太平人寿受产品业务结构变化及假设调整影响，当年新业务CSM下降最明显。</t>
-  </si>
-  <si>
     <t>nb_lost</t>
   </si>
   <si>
     <t>新业务LC</t>
-  </si>
-  <si>
-    <t>9家头部公司中，有6家公司2025年新业务LC有所上升。其中阳光人寿新业务LC上升最多，中国人寿新业务LC下降最多。</t>
   </si>
   <si>
     <t>新业务LC为非PAA合同组的新业务亏损合同金额</t>
@@ -628,11 +546,6 @@
 新业务RA率=新业务RA/新业务未来现金流入的折现值。</t>
   </si>
   <si>
-    <t>太平人寿新业务CSM利润率显著下降，人保寿险和友邦人寿新业务CSM利润率上升较明显，其他头部公司CSM利润率稳定；
-友邦人寿新业务LC亏损率相较去年显著升高。
-太平人寿在新业务RA摊销载体重考虑获取费用，新业务RA比率高于行业平均水平。</t>
-  </si>
-  <si>
     <t>nb_margin_trend</t>
   </si>
   <si>
@@ -657,11 +570,6 @@
     <t xml:space="preserve">下表展示了2025年度和2024年度财务报表中不同集团/保险公司在计量长期人身保险合同所使用的折现率假设的披露情况。折现率上的差异将影响到过渡期计算以及后续新业务的计量。国内上市公司对于不随基础项目回报变动的折现率确定的方法较为一致，均采用“自下而上”的方式。
 披露水平：对于国内的保险公司，折现率的披露较为一致。大多数上市公司披露了即期曲线的最大值和最小值。
 </t>
-  </si>
-  <si>
-    <t>根据可观察到的披露数据，假设以2025/12/31当日国债曲线和4.5%的终极利率作为基础曲线，部分头部公司2025年底不随基础项目回报变动折现率的溢价水平在25-65bps，终极利率溢价水平在10-30bps。
-其他：友邦按国家/地区披露所使用的折现率（基础曲线/基础曲线+溢价），我们选择了中国的折现率进行比较。友邦仅披露了前20年的负债折现率水平。
-太平集团对随基础项目回报而变动的现金流，采用风险中性或真实世界法确定不同产品的折现率。</t>
   </si>
   <si>
     <t>confidence_level</t>
@@ -676,10 +584,6 @@
 我们观察到不同保险公司应用的置信水平相似；但保险集团内子公司可能采用不同的RA计算方法和置信水平，</t>
   </si>
   <si>
-    <t>例如人保寿险在其年度报告中提到，其采用了包括资本成本和置信水平法在内的多种方法。
-平安人寿、太保寿险和阳光人寿披露的非金融风险调整的置信水平包括再保前和分出再保部分（其中，平安人寿和太保寿险均75%，阳光人数为75%~85%）；友邦人寿仅披露再保前非金融风险调整的置信水平，其余公司未披露具体细节。</t>
-  </si>
-  <si>
     <t>csm_maturity_table</t>
   </si>
   <si>
@@ -688,10 +592,6 @@
   <si>
     <t>下方表格提供了2025年度财务报表中不同集团/保险公司未来各日历年度合同服务边际（CSM）确认的预期时间线。
 CSM未来确认时点的披露差异：不同公司在披露合同服务边际未来确认的时间线上存在较大的差异。</t>
-  </si>
-  <si>
-    <t>在年报披露中，友邦、新华和人保披露了未来年度预期确认的CSM绝对金额。
-大多数头部公司前10年CSM摊销比例可比。</t>
   </si>
   <si>
     <t>six_dimensional_charts</t>
@@ -1792,7 +1692,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16317595" y="7891780"/>
+          <a:off x="16317595" y="7353300"/>
           <a:ext cx="9746615" cy="431800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1830,7 +1730,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="16565880" y="9063355"/>
+          <a:off x="16565880" y="8524875"/>
           <a:ext cx="9429750" cy="509905"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -2164,19 +2064,17 @@
         <v>14</v>
       </c>
       <c r="E3" s="9"/>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="10"/>
+      <c r="G3" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="I3" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="11" t="s">
+    </row>
+    <row r="4" ht="41.65" spans="1:19">
+      <c r="A4" s="5" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="4" ht="42.4" spans="1:19">
-      <c r="A4" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>9</v>
@@ -2185,23 +2083,21 @@
         <v>13</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="6"/>
-      <c r="F4" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="F4" s="6"/>
       <c r="G4" s="6"/>
       <c r="H4" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" ht="42.4" spans="1:19">
       <c r="A5" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>9</v>
@@ -2210,227 +2106,211 @@
         <v>13</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>26</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="I5" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" ht="70.15" spans="1:19">
       <c r="A6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="F6" s="6"/>
+      <c r="G6" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="H6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>34</v>
-      </c>
       <c r="I6" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" ht="56.25" spans="1:19">
       <c r="A7" s="5" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>38</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="F7" s="6"/>
       <c r="G7" s="6"/>
       <c r="I7" s="13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" ht="56.25" spans="1:19">
       <c r="A8" s="5" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D8" s="8" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>43</v>
-      </c>
+        <v>37</v>
+      </c>
+      <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="I8" s="13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" ht="70.15" spans="1:19">
       <c r="A9" s="5" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D9" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="H9" s="11" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" ht="56.25" spans="1:19">
       <c r="A10" s="5" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="F10" s="6"/>
       <c r="G10" s="6"/>
       <c r="H10" s="11"/>
       <c r="I10" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" ht="56.25" spans="1:19">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" ht="14.6" spans="1:19">
       <c r="A11" s="5" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D11" s="8" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="E11" s="6"/>
-      <c r="F11" s="6" t="s">
-        <v>54</v>
-      </c>
+      <c r="F11" s="6"/>
       <c r="G11" s="6" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J11" s="13"/>
     </row>
     <row r="12" ht="56.25" spans="1:19">
       <c r="A12" s="5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D12" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>33</v>
-      </c>
       <c r="H12" s="12" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" ht="70.15" spans="1:19">
       <c r="A13" s="5" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D13" s="8" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>64</v>
-      </c>
+        <v>54</v>
+      </c>
+      <c r="F13" s="6"/>
       <c r="G13" s="6"/>
       <c r="H13" s="12" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="J13" s="14"/>
       <c r="K13" s="14">
@@ -2463,27 +2343,25 @@
     </row>
     <row r="14" ht="70.15" spans="1:19">
       <c r="A14" s="5" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>70</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="F14" s="6"/>
       <c r="G14" s="6"/>
       <c r="H14" s="12"/>
       <c r="I14" s="13" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="J14" s="14">
         <f>AVERAGE(K14:S14)</f>
@@ -2519,290 +2397,272 @@
     </row>
     <row r="15" ht="42.4" spans="1:19">
       <c r="A15" s="5" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D15" s="8" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>75</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="F15" s="6"/>
       <c r="G15" s="6"/>
       <c r="I15" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" ht="42.4" spans="1:19">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" ht="27.75" spans="1:19">
       <c r="A16" s="5" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D16" s="8" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>79</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="F16" s="6"/>
       <c r="G16" s="6"/>
       <c r="H16" s="11" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="I16" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="17" ht="42.4" spans="1:10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" ht="27.75" spans="1:10">
       <c r="A17" s="5" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>83</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="F17" s="6"/>
       <c r="G17" s="6"/>
       <c r="I17" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18" ht="42.4" spans="1:10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" ht="27.75" spans="1:10">
       <c r="A18" s="5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="E18" s="7"/>
-      <c r="F18" s="6" t="s">
-        <v>87</v>
-      </c>
+      <c r="F18" s="6"/>
       <c r="G18" s="6"/>
       <c r="I18" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" ht="56.25" spans="1:10">
       <c r="A19" s="5" t="s">
-        <v>88</v>
+        <v>73</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="F19" s="6"/>
       <c r="G19" s="6"/>
     </row>
     <row r="20" ht="70.15" spans="1:10">
       <c r="A20" s="5" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="B20" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>94</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="F20" s="10"/>
       <c r="G20" s="6"/>
       <c r="I20" s="11" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" ht="28.5" spans="1:10">
       <c r="A21" s="5" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="B21" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D21" s="8" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" ht="42.4" spans="1:10">
+    <row r="22" ht="27.75" spans="1:10">
       <c r="A22" s="5" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>100</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="F22" s="6"/>
       <c r="G22" s="6"/>
       <c r="H22" s="12" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="I22" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="23" ht="28.5" spans="1:10">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" ht="27.75" spans="1:10">
       <c r="A23" s="5" t="s">
-        <v>102</v>
+        <v>85</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D23" s="8" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="E23" s="6"/>
-      <c r="F23" s="6" t="s">
-        <v>105</v>
-      </c>
+      <c r="F23" s="6"/>
       <c r="G23" s="6"/>
       <c r="I23" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" ht="97.9" spans="1:10">
       <c r="A24" s="5" t="s">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="D24" s="8" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>109</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="F24" s="12"/>
       <c r="G24" s="15" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" ht="28.5" spans="1:10">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" ht="27.75" spans="1:10">
       <c r="A25" s="5" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D25" s="8" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="E25" s="6"/>
-      <c r="F25" s="6" t="s">
-        <v>114</v>
-      </c>
+      <c r="F25" s="6"/>
       <c r="G25" s="6"/>
       <c r="I25" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" ht="42.4" spans="1:10">
       <c r="A26" s="5" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
       <c r="G26" s="6"/>
       <c r="I26" s="12" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" ht="14.65" spans="1:10">
       <c r="A27" s="5" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D27" s="8" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
@@ -2810,328 +2670,308 @@
     </row>
     <row r="28" ht="42.4" spans="1:10">
       <c r="A28" s="5" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="I28" s="13" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" ht="181.15" spans="1:10">
       <c r="A29" s="5" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>127</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="F29" s="6"/>
       <c r="G29" s="6"/>
       <c r="H29" s="16" t="s">
-        <v>128</v>
+        <v>107</v>
       </c>
       <c r="I29" s="13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J29" s="14"/>
     </row>
     <row r="30" ht="181.15" spans="1:10">
       <c r="A30" s="5" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>131</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="F30" s="6"/>
       <c r="G30" s="6"/>
       <c r="H30" s="16"/>
       <c r="I30" s="13" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="J30" s="14"/>
     </row>
-    <row r="31" ht="84" spans="1:10">
+    <row r="31" ht="75" spans="1:10">
       <c r="A31" s="5" t="s">
-        <v>132</v>
+        <v>110</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C31" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D31" s="17" t="s">
-        <v>133</v>
-      </c>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G31" s="6" t="s">
-        <v>135</v>
-      </c>
       <c r="H31" s="16" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="I31" s="12" t="s">
-        <v>137</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32" ht="28.5" spans="1:10">
       <c r="A32" s="5" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="E32" s="6"/>
-      <c r="F32" s="6" t="s">
-        <v>140</v>
-      </c>
+      <c r="F32" s="6"/>
       <c r="G32" s="6" t="s">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="H32" s="16"/>
       <c r="I32" s="11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" ht="70.15" spans="1:9">
       <c r="A33" s="5" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="D33" s="8" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
       <c r="G33" s="6" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="H33" s="16"/>
       <c r="I33" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="34" ht="56.25" spans="1:9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" ht="27.75" spans="1:9">
       <c r="A34" s="5" t="s">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>147</v>
+        <v>123</v>
       </c>
       <c r="E34" s="6"/>
-      <c r="F34" s="6" t="s">
-        <v>148</v>
-      </c>
+      <c r="F34" s="6"/>
       <c r="G34" s="6"/>
       <c r="H34" s="16"/>
       <c r="I34" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" ht="42.4" spans="1:9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" ht="27.75" spans="1:9">
       <c r="A35" s="5" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>150</v>
-      </c>
-      <c r="F35" s="6" t="s">
-        <v>151</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="F35" s="6"/>
       <c r="G35" s="6" t="s">
-        <v>152</v>
+        <v>126</v>
       </c>
       <c r="H35" s="16"/>
       <c r="I35" s="11" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" ht="97.9" spans="1:9">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" ht="83.25" spans="1:9">
       <c r="A36" s="5" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="D36" s="17" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="F36" s="6" t="s">
-        <v>156</v>
-      </c>
+        <v>129</v>
+      </c>
+      <c r="F36" s="6"/>
       <c r="G36" s="7"/>
       <c r="H36" s="16"/>
       <c r="I36" s="12" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
     </row>
     <row r="37" ht="42.4" spans="1:9">
       <c r="A37" s="5" t="s">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>159</v>
+        <v>132</v>
       </c>
       <c r="F37" s="6"/>
       <c r="G37" s="6" t="s">
-        <v>160</v>
+        <v>133</v>
       </c>
       <c r="H37" s="16"/>
       <c r="I37" s="12" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="38" ht="167.25" spans="1:9">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="38" ht="152.65" spans="1:9">
       <c r="A38" s="5" t="s">
-        <v>161</v>
+        <v>134</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="8" t="s">
-        <v>163</v>
+        <v>136</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>164</v>
-      </c>
-      <c r="F38" s="6" t="s">
-        <v>165</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="16"/>
       <c r="I38" s="16"/>
     </row>
     <row r="39" ht="195" spans="1:9">
       <c r="A39" s="5" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="8" t="s">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>169</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="16"/>
       <c r="I39" s="16"/>
     </row>
     <row r="40" ht="84" spans="1:9">
       <c r="A40" s="5" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>162</v>
+        <v>135</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="8" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>173</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="F40" s="6"/>
       <c r="G40" s="6"/>
       <c r="H40" s="16"/>
       <c r="I40" s="16"/>
     </row>
     <row r="41" ht="42.4" spans="1:9">
       <c r="A41" s="5" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="8" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
@@ -3140,17 +2980,17 @@
     </row>
     <row r="42" ht="28.5" spans="1:9">
       <c r="A42" s="5" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="8" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
@@ -3159,21 +2999,21 @@
     </row>
     <row r="43" ht="54" customHeight="1" spans="1:9">
       <c r="A43" s="8" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="C43" s="8"/>
       <c r="D43" s="8" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="F43" s="18"/>
       <c r="G43" s="6" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="H43" s="16"/>
       <c r="I43" s="16"/>
